--- a/previews/labels.xlsx
+++ b/previews/labels.xlsx
@@ -104,21 +104,54 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:oneCellAnchor>
     <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="800100" cy="800100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="800100" cy="800100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2159000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -139,19 +172,19 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="800100" cy="800100"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
+        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -172,19 +205,19 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2159000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
+        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -205,19 +238,19 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="800100" cy="800100"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId4"/>
+        <xdr:cNvPr id="6" name="Picture 5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -238,19 +271,19 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2159000" cy="381000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId5"/>
+        <xdr:cNvPr id="7" name="Picture 6"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -259,39 +292,6 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="2159000" cy="381000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="800100" cy="800100"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="800100" cy="800100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
